--- a/Deep_Learning/hparams_table.xlsx
+++ b/Deep_Learning/hparams_table.xlsx
@@ -358,7 +358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -385,744 +385,310 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02339310199022293</v>
+        <v>0.01467037107795477</v>
       </c>
       <c r="C2" t="n">
-        <v>0.990587055683136</v>
+        <v>0.9947291612625122</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7015513777732849</v>
+        <v>0.796126663684845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01839782111346722</v>
+        <v>0.01176238339394331</v>
       </c>
       <c r="C3" t="n">
-        <v>0.992647111415863</v>
+        <v>0.9954235553741455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.746595561504364</v>
+        <v>0.8268093466758728</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01400113198906183</v>
+        <v>0.01308712363243103</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9944554567337036</v>
+        <v>0.9950440526008606</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7999396920204163</v>
+        <v>0.8042255640029907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04985303059220314</v>
+        <v>0.01397779677063227</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9821398258209229</v>
+        <v>0.9946508407592773</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5706828832626343</v>
+        <v>0.7965800166130066</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01453210599720478</v>
+        <v>0.01148336473852396</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9944313764572144</v>
+        <v>0.9954444169998169</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7838242650032043</v>
+        <v>0.8223036527633667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01277930289506912</v>
+        <v>0.01251881010830402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.995045006275177</v>
+        <v>0.995384693145752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8035196661949158</v>
+        <v>0.8197834491729736</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02523892372846603</v>
+        <v>0.01431511528789997</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9918892383575439</v>
+        <v>0.9946514964103699</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6342666149139404</v>
+        <v>0.7920565009117126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="B9" t="n">
-        <v>0.06716251373291016</v>
+        <v>0.02249140106141567</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9719123244285583</v>
+        <v>0.9918814897537231</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4551893174648285</v>
+        <v>0.6280805468559265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02499277144670486</v>
+        <v>0.01244823727756739</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9913631677627563</v>
+        <v>0.995165228843689</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7209628224372864</v>
+        <v>0.8081525564193726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01449499931186438</v>
+        <v>0.01399548072367907</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9946507215499878</v>
+        <v>0.994946300983429</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7986832857131958</v>
+        <v>0.8035096526145935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01651012897491455</v>
+        <v>0.01231304835528135</v>
       </c>
       <c r="C12" t="n">
-        <v>0.994550883769989</v>
+        <v>0.99528568983078</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7827951908111572</v>
+        <v>0.8248319029808044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02945904619991779</v>
+        <v>0.01365033071488142</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9887418746948242</v>
+        <v>0.9949947595596313</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6608448624610901</v>
+        <v>0.8103203177452087</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01329626608639956</v>
+        <v>0.01425191853195429</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9948435425758362</v>
+        <v>0.9949615001678467</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7975364327430725</v>
+        <v>0.8077341914176941</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01963365823030472</v>
+        <v>0.01238471362739801</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9931949377059937</v>
+        <v>0.9950904250144958</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7372913956642151</v>
+        <v>0.8131044507026672</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1033905819058418</v>
+        <v>0.01283400505781174</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9496332406997681</v>
+        <v>0.9951179027557373</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3309006094932556</v>
+        <v>0.8228477835655212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06071737036108971</v>
+        <v>0.01113695185631514</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9746928811073303</v>
+        <v>0.9955967664718628</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4774852693080902</v>
+        <v>0.8339800834655762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01403924264013767</v>
+        <v>0.0135407717898488</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9943869113922119</v>
+        <v>0.9950014352798462</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7917769551277161</v>
+        <v>0.7997431755065918</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01499029714614153</v>
+        <v>0.01414352562278509</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9946433901786804</v>
+        <v>0.9945325255393982</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7919573783874512</v>
+        <v>0.7931797504425049</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01590230129659176</v>
+        <v>0.01139825489372015</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9946205019950867</v>
+        <v>0.995410144329071</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7885122299194336</v>
+        <v>0.8237511515617371</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01302154455333948</v>
+        <v>0.01459333579987288</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9949086904525757</v>
+        <v>0.9948922991752625</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8027735948562622</v>
+        <v>0.7995118498802185</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01351886335760355</v>
+        <v>0.01244234759360552</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9949511885643005</v>
+        <v>0.9951004981994629</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8058893084526062</v>
+        <v>0.8046048879623413</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02758633345365524</v>
+        <v>0.01613794080913067</v>
       </c>
       <c r="C23" t="n">
-        <v>0.990420937538147</v>
+        <v>0.9942662715911865</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5739288330078125</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>132</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.0320197232067585</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.9884148240089417</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.6639060974121094</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>164</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.02439636737108231</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.99238520860672</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.747897207736969</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>159</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.01332652010023594</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.994969367980957</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.8053876757621765</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>146</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.0228569358587265</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.9922957420349121</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.7471926808357239</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>151</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.01385446172207594</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.9947907328605652</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.7955393195152283</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>123</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.02990890108048916</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.9907528758049011</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.5639167428016663</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>133</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.01320116687566042</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.9950829744338989</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.7994534373283386</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>165</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.01436861045658588</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.9947771430015564</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.7964836955070496</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>155</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.01687759347259998</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.9943118691444397</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.7700825333595276</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>150</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.01298616267740726</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.9948431253433228</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.8047600984573364</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>139</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0.03210152313113213</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.9912702441215515</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.7027103304862976</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>128</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.01385160256177187</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.9947324395179749</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.7837510704994202</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>152</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.01517419796437025</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.994621217250824</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.7848495841026306</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>114</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.01331145130097866</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.9948261380195618</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.802487313747406</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>115</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0.01225592009723186</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.9952294230461121</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.8142895698547363</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>144</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.0239963810890913</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.9918383359909058</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.6542782783508301</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>122</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.01466464903205633</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.9948285818099976</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.8009670376777649</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>134</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0.03383200243115425</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.9871729612350464</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.63605797290802</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>147</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0.01258653961122036</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.9952071905136108</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.8145135641098022</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>113</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0.01258689537644386</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.9952795505523682</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.819157600402832</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>156</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0.01787486486136913</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.9941992163658142</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.785882830619812</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>136</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0.02560011111199856</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.9904752969741821</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.6781409382820129</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>160</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0.01547244284301996</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.9946091175079346</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.794163703918457</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>130</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0.03845126554369926</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.9832438826560974</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.5795336961746216</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>137</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.01304361317306757</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.9949219226837158</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.7966872453689575</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>116</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.01258875522762537</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.9949671030044556</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.809225857257843</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>124</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0.02378304675221443</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.9909543395042419</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.6966580152511597</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>149</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.024897251278162</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.9915992617607117</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.6298223733901978</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>129</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.02112032286822796</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.993371844291687</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.7632242441177368</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>125</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.01672528684139252</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.9940369725227356</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.7727526426315308</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0.0236707478761673</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.9907107949256897</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.7061039805412292</v>
+        <v>0.7505086660385132</v>
       </c>
     </row>
   </sheetData>
